--- a/output/yearly_population_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_71_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5048</v>
+        <v>4734</v>
       </c>
       <c r="C2" t="n">
-        <v>9363</v>
+        <v>7414</v>
       </c>
       <c r="D2" t="n">
-        <v>23119</v>
+        <v>32384</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3766</v>
+        <v>2759</v>
       </c>
       <c r="C3" t="n">
-        <v>5621</v>
+        <v>8135</v>
       </c>
       <c r="D3" t="n">
-        <v>15974</v>
+        <v>18913</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2723</v>
+        <v>2400</v>
       </c>
       <c r="C4" t="n">
-        <v>5388</v>
+        <v>8367</v>
       </c>
       <c r="D4" t="n">
-        <v>6639</v>
+        <v>8708</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1686</v>
+        <v>1644</v>
       </c>
       <c r="C5" t="n">
-        <v>4786</v>
+        <v>6184</v>
       </c>
       <c r="D5" t="n">
-        <v>2305</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="C6" t="n">
-        <v>3548</v>
+        <v>3770</v>
       </c>
       <c r="D6" t="n">
-        <v>1032</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="C7" t="n">
-        <v>1994</v>
+        <v>1974</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>869</v>
+        <v>947</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>357</v>
+        <v>394</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6046</v>
+        <v>5005</v>
       </c>
       <c r="C2" t="n">
-        <v>15586</v>
+        <v>5575</v>
       </c>
       <c r="D2" t="n">
-        <v>24212</v>
+        <v>27479</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3548</v>
+        <v>2910</v>
       </c>
       <c r="C3" t="n">
-        <v>6443</v>
+        <v>6926</v>
       </c>
       <c r="D3" t="n">
-        <v>15872</v>
+        <v>19396</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2707</v>
+        <v>2184</v>
       </c>
       <c r="C4" t="n">
-        <v>5387</v>
+        <v>8088</v>
       </c>
       <c r="D4" t="n">
-        <v>7960</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1878</v>
+        <v>1749</v>
       </c>
       <c r="C5" t="n">
-        <v>4917</v>
+        <v>6939</v>
       </c>
       <c r="D5" t="n">
-        <v>2878</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1145</v>
+        <v>1107</v>
       </c>
       <c r="C6" t="n">
-        <v>4071</v>
+        <v>4718</v>
       </c>
       <c r="D6" t="n">
-        <v>1213</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="C7" t="n">
-        <v>2658</v>
+        <v>2730</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="C8" t="n">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>564</v>
+        <v>610</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8239</v>
+        <v>5690</v>
       </c>
       <c r="C2" t="n">
-        <v>9805</v>
+        <v>8517</v>
       </c>
       <c r="D2" t="n">
-        <v>21034</v>
+        <v>32730</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3712</v>
+        <v>3012</v>
       </c>
       <c r="C3" t="n">
-        <v>9012</v>
+        <v>5729</v>
       </c>
       <c r="D3" t="n">
-        <v>15856</v>
+        <v>19090</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2624</v>
+        <v>2095</v>
       </c>
       <c r="C4" t="n">
-        <v>5679</v>
+        <v>7373</v>
       </c>
       <c r="D4" t="n">
-        <v>8780</v>
+        <v>10871</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1958</v>
+        <v>1715</v>
       </c>
       <c r="C5" t="n">
-        <v>5013</v>
+        <v>7180</v>
       </c>
       <c r="D5" t="n">
-        <v>3522</v>
+        <v>4499</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1305</v>
+        <v>1228</v>
       </c>
       <c r="C6" t="n">
-        <v>4336</v>
+        <v>5531</v>
       </c>
       <c r="D6" t="n">
-        <v>1409</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>718</v>
+        <v>682</v>
       </c>
       <c r="C7" t="n">
-        <v>3198</v>
+        <v>3442</v>
       </c>
       <c r="D7" t="n">
-        <v>748</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="C8" t="n">
-        <v>1864</v>
+        <v>1835</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="C9" t="n">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7421</v>
+        <v>5276</v>
       </c>
       <c r="C2" t="n">
-        <v>6745</v>
+        <v>5995</v>
       </c>
       <c r="D2" t="n">
-        <v>17588</v>
+        <v>27283</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4575</v>
+        <v>3632</v>
       </c>
       <c r="C3" t="n">
-        <v>12093</v>
+        <v>9573</v>
       </c>
       <c r="D3" t="n">
-        <v>17157</v>
+        <v>20670</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1809</v>
+        <v>1584</v>
       </c>
       <c r="C4" t="n">
-        <v>7920</v>
+        <v>10714</v>
       </c>
       <c r="D4" t="n">
-        <v>8165</v>
+        <v>10145</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1205</v>
+        <v>1134</v>
       </c>
       <c r="C5" t="n">
-        <v>4249</v>
+        <v>5420</v>
       </c>
       <c r="D5" t="n">
-        <v>2327</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>663</v>
+        <v>630</v>
       </c>
       <c r="C6" t="n">
-        <v>3134</v>
+        <v>3373</v>
       </c>
       <c r="D6" t="n">
-        <v>733</v>
+        <v>790</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>1826</v>
+        <v>1798</v>
       </c>
       <c r="D7" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4449</v>
+        <v>3227</v>
       </c>
       <c r="C2" t="n">
-        <v>3139</v>
+        <v>2808</v>
       </c>
       <c r="D2" t="n">
-        <v>12431</v>
+        <v>18748</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4947</v>
+        <v>3708</v>
       </c>
       <c r="C3" t="n">
-        <v>8788</v>
+        <v>7312</v>
       </c>
       <c r="D3" t="n">
-        <v>16392</v>
+        <v>20358</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2481</v>
+        <v>2029</v>
       </c>
       <c r="C4" t="n">
-        <v>9906</v>
+        <v>10295</v>
       </c>
       <c r="D4" t="n">
-        <v>9290</v>
+        <v>11546</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1353</v>
+        <v>1232</v>
       </c>
       <c r="C5" t="n">
-        <v>5879</v>
+        <v>7651</v>
       </c>
       <c r="D5" t="n">
-        <v>3029</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>788</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>3710</v>
+        <v>4248</v>
       </c>
       <c r="D6" t="n">
-        <v>898</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>2314</v>
+        <v>2324</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3968</v>
+        <v>3021</v>
       </c>
       <c r="C2" t="n">
-        <v>3919</v>
+        <v>6121</v>
       </c>
       <c r="D2" t="n">
-        <v>13358</v>
+        <v>27117</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3981</v>
+        <v>2985</v>
       </c>
       <c r="C3" t="n">
-        <v>5414</v>
+        <v>4680</v>
       </c>
       <c r="D3" t="n">
-        <v>14751</v>
+        <v>18966</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3038</v>
+        <v>2321</v>
       </c>
       <c r="C4" t="n">
-        <v>9152</v>
+        <v>8677</v>
       </c>
       <c r="D4" t="n">
-        <v>10166</v>
+        <v>12437</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1615</v>
+        <v>1390</v>
       </c>
       <c r="C5" t="n">
-        <v>7707</v>
+        <v>8758</v>
       </c>
       <c r="D5" t="n">
-        <v>3898</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>932</v>
+        <v>859</v>
       </c>
       <c r="C6" t="n">
-        <v>4632</v>
+        <v>5646</v>
       </c>
       <c r="D6" t="n">
-        <v>1193</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>388</v>
       </c>
       <c r="C7" t="n">
-        <v>2937</v>
+        <v>3137</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1613</v>
+        <v>1589</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
         <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2386</v>
+        <v>1824</v>
       </c>
       <c r="C2" t="n">
-        <v>1840</v>
+        <v>3025</v>
       </c>
       <c r="D2" t="n">
-        <v>9356</v>
+        <v>18886</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3839</v>
+        <v>2916</v>
       </c>
       <c r="C3" t="n">
-        <v>4747</v>
+        <v>4964</v>
       </c>
       <c r="D3" t="n">
-        <v>14275</v>
+        <v>19570</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3342</v>
+        <v>2539</v>
       </c>
       <c r="C4" t="n">
-        <v>8708</v>
+        <v>8184</v>
       </c>
       <c r="D4" t="n">
-        <v>10778</v>
+        <v>13249</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1661</v>
+        <v>1462</v>
       </c>
       <c r="C5" t="n">
-        <v>9146</v>
+        <v>10180</v>
       </c>
       <c r="D5" t="n">
-        <v>4126</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>772</v>
+        <v>691</v>
       </c>
       <c r="C6" t="n">
-        <v>5586</v>
+        <v>6418</v>
       </c>
       <c r="D6" t="n">
-        <v>1176</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>3019</v>
+        <v>3103</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>1156</v>
+        <v>1102</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3162</v>
+        <v>1839</v>
       </c>
       <c r="C2" t="n">
-        <v>7963</v>
+        <v>8346</v>
       </c>
       <c r="D2" t="n">
-        <v>13969</v>
+        <v>14326</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2777</v>
+        <v>2134</v>
       </c>
       <c r="C3" t="n">
-        <v>3060</v>
+        <v>3687</v>
       </c>
       <c r="D3" t="n">
-        <v>12783</v>
+        <v>18198</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3126</v>
+        <v>2346</v>
       </c>
       <c r="C4" t="n">
-        <v>6747</v>
+        <v>6639</v>
       </c>
       <c r="D4" t="n">
-        <v>10987</v>
+        <v>13817</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2055</v>
+        <v>1681</v>
       </c>
       <c r="C5" t="n">
-        <v>8850</v>
+        <v>9222</v>
       </c>
       <c r="D5" t="n">
-        <v>4958</v>
+        <v>6015</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>996</v>
+        <v>884</v>
       </c>
       <c r="C6" t="n">
-        <v>7060</v>
+        <v>7906</v>
       </c>
       <c r="D6" t="n">
-        <v>1557</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="C7" t="n">
-        <v>4053</v>
+        <v>4366</v>
       </c>
       <c r="D7" t="n">
-        <v>639</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1865</v>
+        <v>1809</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2099</v>
+        <v>1315</v>
       </c>
       <c r="C2" t="n">
-        <v>4700</v>
+        <v>4531</v>
       </c>
       <c r="D2" t="n">
-        <v>10106</v>
+        <v>10324</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2541</v>
+        <v>1794</v>
       </c>
       <c r="C3" t="n">
-        <v>4506</v>
+        <v>4927</v>
       </c>
       <c r="D3" t="n">
-        <v>12352</v>
+        <v>16803</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2787</v>
+        <v>2108</v>
       </c>
       <c r="C4" t="n">
-        <v>5314</v>
+        <v>5558</v>
       </c>
       <c r="D4" t="n">
-        <v>10982</v>
+        <v>14076</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2256</v>
+        <v>1782</v>
       </c>
       <c r="C5" t="n">
-        <v>8258</v>
+        <v>8427</v>
       </c>
       <c r="D5" t="n">
-        <v>5491</v>
+        <v>6771</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1169</v>
+        <v>1010</v>
       </c>
       <c r="C6" t="n">
-        <v>7892</v>
+        <v>8621</v>
       </c>
       <c r="D6" t="n">
-        <v>1877</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="C7" t="n">
-        <v>5036</v>
+        <v>5461</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>2378</v>
+        <v>2355</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>644</v>
+        <v>593</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3137</v>
+        <v>1829</v>
       </c>
       <c r="C2" t="n">
-        <v>10020</v>
+        <v>15844</v>
       </c>
       <c r="D2" t="n">
-        <v>15975</v>
+        <v>13457</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2011</v>
+        <v>1377</v>
       </c>
       <c r="C3" t="n">
-        <v>4076</v>
+        <v>4265</v>
       </c>
       <c r="D3" t="n">
-        <v>11291</v>
+        <v>15028</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2348</v>
+        <v>1740</v>
       </c>
       <c r="C4" t="n">
-        <v>4862</v>
+        <v>5187</v>
       </c>
       <c r="D4" t="n">
-        <v>10845</v>
+        <v>14014</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2221</v>
+        <v>1743</v>
       </c>
       <c r="C5" t="n">
-        <v>6899</v>
+        <v>7150</v>
       </c>
       <c r="D5" t="n">
-        <v>6062</v>
+        <v>7411</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1423</v>
+        <v>1168</v>
       </c>
       <c r="C6" t="n">
-        <v>7966</v>
+        <v>8481</v>
       </c>
       <c r="D6" t="n">
-        <v>2304</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>484</v>
+        <v>399</v>
       </c>
       <c r="C7" t="n">
-        <v>6146</v>
+        <v>6573</v>
       </c>
       <c r="D7" t="n">
-        <v>837</v>
+        <v>883</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>3288</v>
+        <v>3412</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1210</v>
+        <v>1133</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5408</v>
+        <v>4194</v>
       </c>
       <c r="C2" t="n">
-        <v>6299</v>
+        <v>8727</v>
       </c>
       <c r="D2" t="n">
-        <v>7751</v>
+        <v>8243</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2268</v>
+        <v>1336</v>
       </c>
       <c r="C2" t="n">
-        <v>5771</v>
+        <v>9379</v>
       </c>
       <c r="D2" t="n">
-        <v>11885</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2724</v>
+        <v>1897</v>
       </c>
       <c r="C3" t="n">
-        <v>5766</v>
+        <v>7112</v>
       </c>
       <c r="D3" t="n">
-        <v>12462</v>
+        <v>16256</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3251</v>
+        <v>2483</v>
       </c>
       <c r="C4" t="n">
-        <v>7244</v>
+        <v>7659</v>
       </c>
       <c r="D4" t="n">
-        <v>11137</v>
+        <v>14155</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1355</v>
+        <v>1095</v>
       </c>
       <c r="C5" t="n">
-        <v>10760</v>
+        <v>11276</v>
       </c>
       <c r="D5" t="n">
-        <v>5493</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>447</v>
+        <v>368</v>
       </c>
       <c r="C6" t="n">
-        <v>7506</v>
+        <v>7937</v>
       </c>
       <c r="D6" t="n">
-        <v>1842</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>3222</v>
+        <v>3343</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1185</v>
+        <v>1110</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5919</v>
+        <v>7195</v>
       </c>
       <c r="C2" t="n">
-        <v>5319</v>
+        <v>7285</v>
       </c>
       <c r="D2" t="n">
-        <v>8891</v>
+        <v>29365</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2298</v>
+        <v>1783</v>
       </c>
       <c r="C3" t="n">
-        <v>3174</v>
+        <v>4398</v>
       </c>
       <c r="D3" t="n">
-        <v>1941</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4143</v>
+        <v>4467</v>
       </c>
       <c r="C2" t="n">
-        <v>10315</v>
+        <v>4758</v>
       </c>
       <c r="D2" t="n">
-        <v>16779</v>
+        <v>23338</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3374</v>
+        <v>3679</v>
       </c>
       <c r="C3" t="n">
-        <v>3796</v>
+        <v>5201</v>
       </c>
       <c r="D3" t="n">
-        <v>2965</v>
+        <v>6468</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1032</v>
+        <v>809</v>
       </c>
       <c r="C4" t="n">
-        <v>1932</v>
+        <v>2620</v>
       </c>
       <c r="D4" t="n">
-        <v>1572</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4801</v>
+        <v>5229</v>
       </c>
       <c r="C2" t="n">
-        <v>8037</v>
+        <v>9901</v>
       </c>
       <c r="D2" t="n">
-        <v>17678</v>
+        <v>26438</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3090</v>
+        <v>3349</v>
       </c>
       <c r="C3" t="n">
-        <v>6362</v>
+        <v>4342</v>
       </c>
       <c r="D3" t="n">
-        <v>4961</v>
+        <v>8701</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1865</v>
+        <v>1901</v>
       </c>
       <c r="C4" t="n">
-        <v>2947</v>
+        <v>3977</v>
       </c>
       <c r="D4" t="n">
-        <v>1791</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>484</v>
+        <v>385</v>
       </c>
       <c r="C5" t="n">
-        <v>1150</v>
+        <v>1529</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4997</v>
+        <v>5423</v>
       </c>
       <c r="C2" t="n">
-        <v>7727</v>
+        <v>14058</v>
       </c>
       <c r="D2" t="n">
-        <v>24336</v>
+        <v>26159</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3200</v>
+        <v>3465</v>
       </c>
       <c r="C3" t="n">
-        <v>6352</v>
+        <v>6269</v>
       </c>
       <c r="D3" t="n">
-        <v>6544</v>
+        <v>10784</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2095</v>
+        <v>2203</v>
       </c>
       <c r="C4" t="n">
-        <v>4693</v>
+        <v>4090</v>
       </c>
       <c r="D4" t="n">
-        <v>2297</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>981</v>
+        <v>931</v>
       </c>
       <c r="C5" t="n">
-        <v>2074</v>
+        <v>2766</v>
       </c>
       <c r="D5" t="n">
-        <v>1277</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="C6" t="n">
-        <v>730</v>
+        <v>909</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6570</v>
+        <v>5086</v>
       </c>
       <c r="C2" t="n">
-        <v>7135</v>
+        <v>11821</v>
       </c>
       <c r="D2" t="n">
-        <v>37226</v>
+        <v>38310</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2960</v>
+        <v>3233</v>
       </c>
       <c r="C3" t="n">
-        <v>5779</v>
+        <v>8338</v>
       </c>
       <c r="D3" t="n">
-        <v>8266</v>
+        <v>11630</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1632</v>
+        <v>1735</v>
       </c>
       <c r="C4" t="n">
-        <v>4558</v>
+        <v>4280</v>
       </c>
       <c r="D4" t="n">
-        <v>2599</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C5" t="n">
-        <v>2531</v>
+        <v>2519</v>
       </c>
       <c r="D5" t="n">
-        <v>1154</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="C6" t="n">
-        <v>943</v>
+        <v>1230</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>345</v>
+        <v>393</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
         <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5627</v>
+        <v>4781</v>
       </c>
       <c r="C2" t="n">
-        <v>7491</v>
+        <v>12406</v>
       </c>
       <c r="D2" t="n">
-        <v>31075</v>
+        <v>38727</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3970</v>
+        <v>3437</v>
       </c>
       <c r="C3" t="n">
-        <v>5648</v>
+        <v>8904</v>
       </c>
       <c r="D3" t="n">
-        <v>12522</v>
+        <v>15256</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2017</v>
+        <v>2171</v>
       </c>
       <c r="C4" t="n">
-        <v>5157</v>
+        <v>6606</v>
       </c>
       <c r="D4" t="n">
-        <v>3637</v>
+        <v>5527</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1080</v>
+        <v>1126</v>
       </c>
       <c r="C5" t="n">
-        <v>3684</v>
+        <v>3480</v>
       </c>
       <c r="D5" t="n">
-        <v>1410</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="C6" t="n">
-        <v>1845</v>
+        <v>1932</v>
       </c>
       <c r="D6" t="n">
-        <v>820</v>
+        <v>880</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>684</v>
+        <v>848</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>131</v>
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5348</v>
+        <v>3293</v>
       </c>
       <c r="C2" t="n">
-        <v>7127</v>
+        <v>9220</v>
       </c>
       <c r="D2" t="n">
-        <v>31183</v>
+        <v>34317</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3930</v>
+        <v>3349</v>
       </c>
       <c r="C3" t="n">
-        <v>5758</v>
+        <v>9332</v>
       </c>
       <c r="D3" t="n">
-        <v>14588</v>
+        <v>17749</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>2375</v>
       </c>
       <c r="C4" t="n">
-        <v>5327</v>
+        <v>7726</v>
       </c>
       <c r="D4" t="n">
-        <v>5232</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1433</v>
       </c>
       <c r="C5" t="n">
-        <v>4413</v>
+        <v>5058</v>
       </c>
       <c r="D5" t="n">
-        <v>1759</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="C6" t="n">
-        <v>2776</v>
+        <v>2679</v>
       </c>
       <c r="D6" t="n">
-        <v>916</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>1298</v>
+        <v>1400</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>490</v>
+        <v>576</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_71_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4734</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="n">
-        <v>7414</v>
+        <v>8240</v>
       </c>
       <c r="D2" t="n">
-        <v>32384</v>
+        <v>25734</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2759</v>
+        <v>3501</v>
       </c>
       <c r="C3" t="n">
-        <v>8135</v>
+        <v>5554</v>
       </c>
       <c r="D3" t="n">
-        <v>18913</v>
+        <v>19223</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2400</v>
+        <v>2519</v>
       </c>
       <c r="C4" t="n">
-        <v>8367</v>
+        <v>4944</v>
       </c>
       <c r="D4" t="n">
-        <v>8708</v>
+        <v>9805</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1644</v>
+        <v>1738</v>
       </c>
       <c r="C5" t="n">
-        <v>6184</v>
+        <v>4171</v>
       </c>
       <c r="D5" t="n">
-        <v>3145</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>933</v>
+        <v>1010</v>
       </c>
       <c r="C6" t="n">
-        <v>3770</v>
+        <v>2740</v>
       </c>
       <c r="D6" t="n">
-        <v>1231</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="C7" t="n">
-        <v>1974</v>
+        <v>1602</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>947</v>
+        <v>752</v>
       </c>
       <c r="D8" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5005</v>
+        <v>6380</v>
       </c>
       <c r="C2" t="n">
-        <v>5575</v>
+        <v>11011</v>
       </c>
       <c r="D2" t="n">
-        <v>27479</v>
+        <v>38177</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2910</v>
+        <v>3462</v>
       </c>
       <c r="C3" t="n">
-        <v>6926</v>
+        <v>5949</v>
       </c>
       <c r="D3" t="n">
-        <v>19396</v>
+        <v>18816</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2184</v>
+        <v>2510</v>
       </c>
       <c r="C4" t="n">
-        <v>8088</v>
+        <v>5080</v>
       </c>
       <c r="D4" t="n">
-        <v>10010</v>
+        <v>11043</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1749</v>
+        <v>1854</v>
       </c>
       <c r="C5" t="n">
-        <v>6939</v>
+        <v>4440</v>
       </c>
       <c r="D5" t="n">
-        <v>3820</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1107</v>
+        <v>1198</v>
       </c>
       <c r="C6" t="n">
-        <v>4718</v>
+        <v>3318</v>
       </c>
       <c r="D6" t="n">
-        <v>1490</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>557</v>
+        <v>610</v>
       </c>
       <c r="C7" t="n">
-        <v>2730</v>
+        <v>2103</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>793</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C8" t="n">
-        <v>1349</v>
+        <v>1102</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>610</v>
+        <v>512</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1237,7 +1237,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5690</v>
+        <v>7636</v>
       </c>
       <c r="C2" t="n">
-        <v>8517</v>
+        <v>10560</v>
       </c>
       <c r="D2" t="n">
-        <v>32730</v>
+        <v>34387</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3012</v>
+        <v>3746</v>
       </c>
       <c r="C3" t="n">
-        <v>5729</v>
+        <v>7105</v>
       </c>
       <c r="D3" t="n">
-        <v>19090</v>
+        <v>19935</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2095</v>
+        <v>2460</v>
       </c>
       <c r="C4" t="n">
-        <v>7373</v>
+        <v>5349</v>
       </c>
       <c r="D4" t="n">
-        <v>10871</v>
+        <v>11720</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1715</v>
+        <v>1883</v>
       </c>
       <c r="C5" t="n">
-        <v>7180</v>
+        <v>4569</v>
       </c>
       <c r="D5" t="n">
-        <v>4499</v>
+        <v>5335</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1228</v>
+        <v>1330</v>
       </c>
       <c r="C6" t="n">
-        <v>5531</v>
+        <v>3708</v>
       </c>
       <c r="D6" t="n">
-        <v>1783</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>682</v>
+        <v>754</v>
       </c>
       <c r="C7" t="n">
-        <v>3442</v>
+        <v>2590</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>916</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="C8" t="n">
-        <v>1835</v>
+        <v>1473</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>864</v>
+        <v>726</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
         <v>252</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5276</v>
+        <v>6946</v>
       </c>
       <c r="C2" t="n">
-        <v>5995</v>
+        <v>7265</v>
       </c>
       <c r="D2" t="n">
-        <v>27283</v>
+        <v>28466</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3632</v>
+        <v>4457</v>
       </c>
       <c r="C3" t="n">
-        <v>9573</v>
+        <v>10211</v>
       </c>
       <c r="D3" t="n">
-        <v>20670</v>
+        <v>21781</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1584</v>
+        <v>1739</v>
       </c>
       <c r="C4" t="n">
-        <v>10714</v>
+        <v>7313</v>
       </c>
       <c r="D4" t="n">
-        <v>10145</v>
+        <v>11338</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1134</v>
+        <v>1228</v>
       </c>
       <c r="C5" t="n">
-        <v>5420</v>
+        <v>3633</v>
       </c>
       <c r="D5" t="n">
-        <v>2913</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>630</v>
+        <v>696</v>
       </c>
       <c r="C6" t="n">
-        <v>3373</v>
+        <v>2538</v>
       </c>
       <c r="D6" t="n">
-        <v>790</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>1798</v>
+        <v>1443</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>846</v>
+        <v>711</v>
       </c>
       <c r="D8" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
         <v>246</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
         <v>79</v>
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3227</v>
+        <v>4094</v>
       </c>
       <c r="C2" t="n">
-        <v>2808</v>
+        <v>3378</v>
       </c>
       <c r="D2" t="n">
-        <v>18748</v>
+        <v>19501</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3708</v>
+        <v>4728</v>
       </c>
       <c r="C3" t="n">
-        <v>7312</v>
+        <v>8061</v>
       </c>
       <c r="D3" t="n">
-        <v>20358</v>
+        <v>21644</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2029</v>
+        <v>2402</v>
       </c>
       <c r="C4" t="n">
-        <v>10295</v>
+        <v>8777</v>
       </c>
       <c r="D4" t="n">
-        <v>11546</v>
+        <v>12605</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1232</v>
+        <v>1357</v>
       </c>
       <c r="C5" t="n">
-        <v>7651</v>
+        <v>5215</v>
       </c>
       <c r="D5" t="n">
-        <v>3713</v>
+        <v>4419</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>825</v>
       </c>
       <c r="C6" t="n">
-        <v>4248</v>
+        <v>3036</v>
       </c>
       <c r="D6" t="n">
-        <v>987</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>2324</v>
+        <v>1859</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>1118</v>
+        <v>929</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3021</v>
+        <v>4801</v>
       </c>
       <c r="C2" t="n">
-        <v>6121</v>
+        <v>4421</v>
       </c>
       <c r="D2" t="n">
-        <v>27117</v>
+        <v>21086</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2985</v>
+        <v>3752</v>
       </c>
       <c r="C3" t="n">
-        <v>4680</v>
+        <v>5170</v>
       </c>
       <c r="D3" t="n">
-        <v>18966</v>
+        <v>19898</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>2920</v>
       </c>
       <c r="C4" t="n">
-        <v>8677</v>
+        <v>8328</v>
       </c>
       <c r="D4" t="n">
-        <v>12437</v>
+        <v>13696</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1390</v>
+        <v>1592</v>
       </c>
       <c r="C5" t="n">
-        <v>8758</v>
+        <v>6747</v>
       </c>
       <c r="D5" t="n">
-        <v>4803</v>
+        <v>5542</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>859</v>
+        <v>957</v>
       </c>
       <c r="C6" t="n">
-        <v>5646</v>
+        <v>3969</v>
       </c>
       <c r="D6" t="n">
-        <v>1366</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="C7" t="n">
-        <v>3137</v>
+        <v>2383</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
-        <v>1589</v>
+        <v>1311</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>664</v>
+        <v>596</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1824</v>
+        <v>2863</v>
       </c>
       <c r="C2" t="n">
-        <v>3025</v>
+        <v>2063</v>
       </c>
       <c r="D2" t="n">
-        <v>18886</v>
+        <v>14731</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2916</v>
+        <v>3856</v>
       </c>
       <c r="C3" t="n">
-        <v>4964</v>
+        <v>4761</v>
       </c>
       <c r="D3" t="n">
-        <v>19570</v>
+        <v>19575</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2539</v>
+        <v>3212</v>
       </c>
       <c r="C4" t="n">
-        <v>8184</v>
+        <v>8003</v>
       </c>
       <c r="D4" t="n">
-        <v>13249</v>
+        <v>14526</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1462</v>
+        <v>1657</v>
       </c>
       <c r="C5" t="n">
-        <v>10180</v>
+        <v>8065</v>
       </c>
       <c r="D5" t="n">
-        <v>4918</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>691</v>
+        <v>795</v>
       </c>
       <c r="C6" t="n">
-        <v>6418</v>
+        <v>4750</v>
       </c>
       <c r="D6" t="n">
-        <v>1319</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>3103</v>
+        <v>2451</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1102</v>
+        <v>982</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1839</v>
+        <v>3329</v>
       </c>
       <c r="C2" t="n">
-        <v>8346</v>
+        <v>5232</v>
       </c>
       <c r="D2" t="n">
-        <v>14326</v>
+        <v>14529</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2134</v>
+        <v>2920</v>
       </c>
       <c r="C3" t="n">
-        <v>3687</v>
+        <v>3156</v>
       </c>
       <c r="D3" t="n">
-        <v>18198</v>
+        <v>17788</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2346</v>
+        <v>3060</v>
       </c>
       <c r="C4" t="n">
-        <v>6639</v>
+        <v>6388</v>
       </c>
       <c r="D4" t="n">
-        <v>13817</v>
+        <v>14859</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1681</v>
+        <v>2014</v>
       </c>
       <c r="C5" t="n">
-        <v>9222</v>
+        <v>7947</v>
       </c>
       <c r="D5" t="n">
-        <v>6015</v>
+        <v>6909</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>884</v>
+        <v>1018</v>
       </c>
       <c r="C6" t="n">
-        <v>7906</v>
+        <v>6122</v>
       </c>
       <c r="D6" t="n">
-        <v>1751</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>4366</v>
+        <v>3399</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1809</v>
+        <v>1519</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1315</v>
+        <v>2258</v>
       </c>
       <c r="C2" t="n">
-        <v>4531</v>
+        <v>2960</v>
       </c>
       <c r="D2" t="n">
-        <v>10324</v>
+        <v>11374</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1794</v>
+        <v>2673</v>
       </c>
       <c r="C3" t="n">
-        <v>4927</v>
+        <v>3598</v>
       </c>
       <c r="D3" t="n">
-        <v>16803</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2108</v>
+        <v>2779</v>
       </c>
       <c r="C4" t="n">
-        <v>5558</v>
+        <v>5135</v>
       </c>
       <c r="D4" t="n">
-        <v>14076</v>
+        <v>14915</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1782</v>
+        <v>2211</v>
       </c>
       <c r="C5" t="n">
-        <v>8427</v>
+        <v>7533</v>
       </c>
       <c r="D5" t="n">
-        <v>6771</v>
+        <v>7604</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1010</v>
+        <v>1185</v>
       </c>
       <c r="C6" t="n">
-        <v>8621</v>
+        <v>6924</v>
       </c>
       <c r="D6" t="n">
-        <v>2092</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>5461</v>
+        <v>4271</v>
       </c>
       <c r="D7" t="n">
-        <v>731</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2355</v>
+        <v>1953</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1829</v>
+        <v>3426</v>
       </c>
       <c r="C2" t="n">
-        <v>15844</v>
+        <v>5012</v>
       </c>
       <c r="D2" t="n">
-        <v>13457</v>
+        <v>13034</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1377</v>
+        <v>2130</v>
       </c>
       <c r="C3" t="n">
-        <v>4265</v>
+        <v>2976</v>
       </c>
       <c r="D3" t="n">
-        <v>15028</v>
+        <v>14910</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1740</v>
+        <v>2383</v>
       </c>
       <c r="C4" t="n">
-        <v>5187</v>
+        <v>4378</v>
       </c>
       <c r="D4" t="n">
-        <v>14014</v>
+        <v>14704</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1743</v>
+        <v>2190</v>
       </c>
       <c r="C5" t="n">
-        <v>7150</v>
+        <v>6409</v>
       </c>
       <c r="D5" t="n">
-        <v>7411</v>
+        <v>8355</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1168</v>
+        <v>1421</v>
       </c>
       <c r="C6" t="n">
-        <v>8481</v>
+        <v>7099</v>
       </c>
       <c r="D6" t="n">
-        <v>2649</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>399</v>
+        <v>487</v>
       </c>
       <c r="C7" t="n">
-        <v>6573</v>
+        <v>5299</v>
       </c>
       <c r="D7" t="n">
-        <v>883</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>3412</v>
+        <v>2747</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1133</v>
+        <v>1023</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D10" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4194</v>
+        <v>5161</v>
       </c>
       <c r="C2" t="n">
-        <v>8727</v>
+        <v>6356</v>
       </c>
       <c r="D2" t="n">
-        <v>8243</v>
+        <v>18276</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1336</v>
+        <v>2450</v>
       </c>
       <c r="C2" t="n">
-        <v>9379</v>
+        <v>2886</v>
       </c>
       <c r="D2" t="n">
-        <v>10013</v>
+        <v>9594</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1897</v>
+        <v>2887</v>
       </c>
       <c r="C3" t="n">
-        <v>7112</v>
+        <v>3693</v>
       </c>
       <c r="D3" t="n">
-        <v>16256</v>
+        <v>16135</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2483</v>
+        <v>3241</v>
       </c>
       <c r="C4" t="n">
-        <v>7659</v>
+        <v>6518</v>
       </c>
       <c r="D4" t="n">
-        <v>14155</v>
+        <v>15132</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1095</v>
+        <v>1353</v>
       </c>
       <c r="C5" t="n">
-        <v>11276</v>
+        <v>9687</v>
       </c>
       <c r="D5" t="n">
-        <v>6659</v>
+        <v>7563</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>368</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>7937</v>
+        <v>6584</v>
       </c>
       <c r="D6" t="n">
-        <v>2033</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>3343</v>
+        <v>2692</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1110</v>
+        <v>1002</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D13" t="n">
         <v>36</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7195</v>
+        <v>6221</v>
       </c>
       <c r="C2" t="n">
-        <v>7285</v>
+        <v>5151</v>
       </c>
       <c r="D2" t="n">
-        <v>29365</v>
+        <v>33152</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1783</v>
+        <v>2193</v>
       </c>
       <c r="C3" t="n">
-        <v>4398</v>
+        <v>3203</v>
       </c>
       <c r="D3" t="n">
-        <v>2024</v>
+        <v>3709</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4467</v>
+        <v>4753</v>
       </c>
       <c r="C2" t="n">
-        <v>4758</v>
+        <v>5049</v>
       </c>
       <c r="D2" t="n">
-        <v>23338</v>
+        <v>28277</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3679</v>
+        <v>3453</v>
       </c>
       <c r="C3" t="n">
-        <v>5201</v>
+        <v>3712</v>
       </c>
       <c r="D3" t="n">
-        <v>6468</v>
+        <v>8382</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>809</v>
+        <v>987</v>
       </c>
       <c r="C4" t="n">
-        <v>2620</v>
+        <v>1921</v>
       </c>
       <c r="D4" t="n">
-        <v>1589</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5229</v>
+        <v>6185</v>
       </c>
       <c r="C2" t="n">
-        <v>9901</v>
+        <v>7271</v>
       </c>
       <c r="D2" t="n">
-        <v>26438</v>
+        <v>22784</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3349</v>
+        <v>3363</v>
       </c>
       <c r="C3" t="n">
-        <v>4342</v>
+        <v>3839</v>
       </c>
       <c r="D3" t="n">
-        <v>8701</v>
+        <v>10961</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1901</v>
+        <v>1887</v>
       </c>
       <c r="C4" t="n">
-        <v>3977</v>
+        <v>2859</v>
       </c>
       <c r="D4" t="n">
-        <v>2477</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>385</v>
+        <v>457</v>
       </c>
       <c r="C5" t="n">
-        <v>1529</v>
+        <v>1148</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5423</v>
+        <v>5471</v>
       </c>
       <c r="C2" t="n">
-        <v>14058</v>
+        <v>6906</v>
       </c>
       <c r="D2" t="n">
-        <v>26159</v>
+        <v>30668</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3465</v>
+        <v>3823</v>
       </c>
       <c r="C3" t="n">
-        <v>6269</v>
+        <v>4879</v>
       </c>
       <c r="D3" t="n">
-        <v>10784</v>
+        <v>11986</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="C4" t="n">
-        <v>4090</v>
+        <v>3326</v>
       </c>
       <c r="D4" t="n">
-        <v>3536</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>931</v>
+        <v>964</v>
       </c>
       <c r="C5" t="n">
-        <v>2766</v>
+        <v>2011</v>
       </c>
       <c r="D5" t="n">
-        <v>1389</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>909</v>
+        <v>720</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5086</v>
+        <v>5532</v>
       </c>
       <c r="C2" t="n">
-        <v>11821</v>
+        <v>8155</v>
       </c>
       <c r="D2" t="n">
-        <v>38310</v>
+        <v>42138</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3233</v>
+        <v>3364</v>
       </c>
       <c r="C3" t="n">
-        <v>8338</v>
+        <v>4845</v>
       </c>
       <c r="D3" t="n">
-        <v>11630</v>
+        <v>13154</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1735</v>
+        <v>1867</v>
       </c>
       <c r="C4" t="n">
-        <v>4280</v>
+        <v>3425</v>
       </c>
       <c r="D4" t="n">
-        <v>4145</v>
+        <v>4958</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="C5" t="n">
-        <v>2519</v>
+        <v>1966</v>
       </c>
       <c r="D5" t="n">
-        <v>1380</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>1230</v>
+        <v>909</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>393</v>
+        <v>341</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4781</v>
+        <v>4534</v>
       </c>
       <c r="C2" t="n">
-        <v>12406</v>
+        <v>5865</v>
       </c>
       <c r="D2" t="n">
-        <v>38727</v>
+        <v>37652</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3437</v>
+        <v>3677</v>
       </c>
       <c r="C3" t="n">
-        <v>8904</v>
+        <v>5831</v>
       </c>
       <c r="D3" t="n">
-        <v>15256</v>
+        <v>17055</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2171</v>
+        <v>2269</v>
       </c>
       <c r="C4" t="n">
-        <v>6606</v>
+        <v>4212</v>
       </c>
       <c r="D4" t="n">
-        <v>5527</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1126</v>
+        <v>1196</v>
       </c>
       <c r="C5" t="n">
-        <v>3480</v>
+        <v>2779</v>
       </c>
       <c r="D5" t="n">
-        <v>1855</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="C6" t="n">
-        <v>1932</v>
+        <v>1496</v>
       </c>
       <c r="D6" t="n">
-        <v>880</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>848</v>
+        <v>658</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3293</v>
+        <v>5340</v>
       </c>
       <c r="C2" t="n">
-        <v>9220</v>
+        <v>7674</v>
       </c>
       <c r="D2" t="n">
-        <v>34317</v>
+        <v>28962</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3349</v>
+        <v>3370</v>
       </c>
       <c r="C3" t="n">
-        <v>9332</v>
+        <v>5072</v>
       </c>
       <c r="D3" t="n">
-        <v>17749</v>
+        <v>19122</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2375</v>
+        <v>2528</v>
       </c>
       <c r="C4" t="n">
-        <v>7726</v>
+        <v>5025</v>
       </c>
       <c r="D4" t="n">
-        <v>7080</v>
+        <v>8259</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1433</v>
+        <v>1516</v>
       </c>
       <c r="C5" t="n">
-        <v>5058</v>
+        <v>3464</v>
       </c>
       <c r="D5" t="n">
-        <v>2468</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>716</v>
+        <v>761</v>
       </c>
       <c r="C6" t="n">
-        <v>2679</v>
+        <v>2156</v>
       </c>
       <c r="D6" t="n">
-        <v>1036</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C7" t="n">
-        <v>1400</v>
+        <v>1092</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>576</v>
+        <v>471</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">

--- a/output/yearly_population_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_71_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>1266</v>
       </c>
       <c r="C2" t="n">
-        <v>8240</v>
+        <v>4274</v>
       </c>
       <c r="D2" t="n">
-        <v>25734</v>
+        <v>14381</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3501</v>
+        <v>2041</v>
       </c>
       <c r="C3" t="n">
-        <v>5554</v>
+        <v>10551</v>
       </c>
       <c r="D3" t="n">
-        <v>19223</v>
+        <v>13903</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2519</v>
+        <v>1234</v>
       </c>
       <c r="C4" t="n">
-        <v>4944</v>
+        <v>12219</v>
       </c>
       <c r="D4" t="n">
-        <v>9805</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1738</v>
+        <v>605</v>
       </c>
       <c r="C5" t="n">
-        <v>4171</v>
+        <v>7741</v>
       </c>
       <c r="D5" t="n">
-        <v>3759</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1010</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>2740</v>
+        <v>3224</v>
       </c>
       <c r="D6" t="n">
-        <v>1411</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>448</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>1602</v>
+        <v>1020</v>
       </c>
       <c r="D7" t="n">
-        <v>703</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>752</v>
+        <v>369</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6380</v>
+        <v>1476</v>
       </c>
       <c r="C2" t="n">
-        <v>11011</v>
+        <v>11548</v>
       </c>
       <c r="D2" t="n">
-        <v>38177</v>
+        <v>19414</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3462</v>
+        <v>1436</v>
       </c>
       <c r="C3" t="n">
-        <v>5949</v>
+        <v>6606</v>
       </c>
       <c r="D3" t="n">
-        <v>18816</v>
+        <v>13015</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2510</v>
+        <v>1378</v>
       </c>
       <c r="C4" t="n">
-        <v>5080</v>
+        <v>11233</v>
       </c>
       <c r="D4" t="n">
-        <v>11043</v>
+        <v>7366</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1854</v>
+        <v>772</v>
       </c>
       <c r="C5" t="n">
-        <v>4440</v>
+        <v>9729</v>
       </c>
       <c r="D5" t="n">
-        <v>4537</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1198</v>
+        <v>364</v>
       </c>
       <c r="C6" t="n">
-        <v>3318</v>
+        <v>5304</v>
       </c>
       <c r="D6" t="n">
-        <v>1752</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>610</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2103</v>
+        <v>2001</v>
       </c>
       <c r="D7" t="n">
-        <v>793</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1102</v>
+        <v>640</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>512</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7636</v>
+        <v>827</v>
       </c>
       <c r="C2" t="n">
-        <v>10560</v>
+        <v>5225</v>
       </c>
       <c r="D2" t="n">
-        <v>34387</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3746</v>
+        <v>1394</v>
       </c>
       <c r="C3" t="n">
-        <v>7105</v>
+        <v>8123</v>
       </c>
       <c r="D3" t="n">
-        <v>19935</v>
+        <v>13419</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2460</v>
+        <v>1493</v>
       </c>
       <c r="C4" t="n">
-        <v>5349</v>
+        <v>10586</v>
       </c>
       <c r="D4" t="n">
-        <v>11720</v>
+        <v>8037</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1883</v>
+        <v>762</v>
       </c>
       <c r="C5" t="n">
-        <v>4569</v>
+        <v>11374</v>
       </c>
       <c r="D5" t="n">
-        <v>5335</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1330</v>
+        <v>279</v>
       </c>
       <c r="C6" t="n">
-        <v>3708</v>
+        <v>6251</v>
       </c>
       <c r="D6" t="n">
-        <v>2086</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>754</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>2590</v>
+        <v>1779</v>
       </c>
       <c r="D7" t="n">
-        <v>916</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>344</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1473</v>
+        <v>501</v>
       </c>
       <c r="D8" t="n">
-        <v>500</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>726</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6946</v>
+        <v>729</v>
       </c>
       <c r="C2" t="n">
-        <v>7265</v>
+        <v>7031</v>
       </c>
       <c r="D2" t="n">
-        <v>28466</v>
+        <v>11729</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4457</v>
+        <v>990</v>
       </c>
       <c r="C3" t="n">
-        <v>10211</v>
+        <v>6030</v>
       </c>
       <c r="D3" t="n">
-        <v>21781</v>
+        <v>12513</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1739</v>
+        <v>1289</v>
       </c>
       <c r="C4" t="n">
-        <v>7313</v>
+        <v>9285</v>
       </c>
       <c r="D4" t="n">
-        <v>11338</v>
+        <v>8671</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1228</v>
+        <v>936</v>
       </c>
       <c r="C5" t="n">
-        <v>3633</v>
+        <v>10891</v>
       </c>
       <c r="D5" t="n">
-        <v>3478</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>696</v>
+        <v>413</v>
       </c>
       <c r="C6" t="n">
-        <v>2538</v>
+        <v>8418</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>1443</v>
+        <v>3610</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>711</v>
+        <v>974</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>67</v>
-      </c>
-      <c r="D14" t="n">
-        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4094</v>
+        <v>510</v>
       </c>
       <c r="C2" t="n">
-        <v>3378</v>
+        <v>5662</v>
       </c>
       <c r="D2" t="n">
-        <v>19501</v>
+        <v>9421</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4728</v>
+        <v>794</v>
       </c>
       <c r="C3" t="n">
-        <v>8061</v>
+        <v>5830</v>
       </c>
       <c r="D3" t="n">
-        <v>21644</v>
+        <v>11738</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2402</v>
+        <v>1098</v>
       </c>
       <c r="C4" t="n">
-        <v>8777</v>
+        <v>8015</v>
       </c>
       <c r="D4" t="n">
-        <v>12605</v>
+        <v>9007</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1357</v>
+        <v>1005</v>
       </c>
       <c r="C5" t="n">
-        <v>5215</v>
+        <v>10496</v>
       </c>
       <c r="D5" t="n">
-        <v>4419</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>825</v>
+        <v>502</v>
       </c>
       <c r="C6" t="n">
-        <v>3036</v>
+        <v>9532</v>
       </c>
       <c r="D6" t="n">
-        <v>1160</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>1859</v>
+        <v>5034</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>929</v>
+        <v>1498</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4801</v>
+        <v>672</v>
       </c>
       <c r="C2" t="n">
-        <v>4421</v>
+        <v>11774</v>
       </c>
       <c r="D2" t="n">
-        <v>21086</v>
+        <v>14209</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3752</v>
+        <v>583</v>
       </c>
       <c r="C3" t="n">
-        <v>5170</v>
+        <v>5172</v>
       </c>
       <c r="D3" t="n">
-        <v>19898</v>
+        <v>10708</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2920</v>
+        <v>870</v>
       </c>
       <c r="C4" t="n">
-        <v>8328</v>
+        <v>6925</v>
       </c>
       <c r="D4" t="n">
-        <v>13696</v>
+        <v>9126</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1592</v>
+        <v>949</v>
       </c>
       <c r="C5" t="n">
-        <v>6747</v>
+        <v>9277</v>
       </c>
       <c r="D5" t="n">
-        <v>5542</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>957</v>
+        <v>621</v>
       </c>
       <c r="C6" t="n">
-        <v>3969</v>
+        <v>9822</v>
       </c>
       <c r="D6" t="n">
-        <v>1613</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>2383</v>
+        <v>6756</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>727</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1311</v>
+        <v>2710</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>745</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2863</v>
+        <v>483</v>
       </c>
       <c r="C2" t="n">
-        <v>2063</v>
+        <v>6781</v>
       </c>
       <c r="D2" t="n">
-        <v>14731</v>
+        <v>10458</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3856</v>
+        <v>832</v>
       </c>
       <c r="C3" t="n">
-        <v>4761</v>
+        <v>7105</v>
       </c>
       <c r="D3" t="n">
-        <v>19575</v>
+        <v>11802</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3212</v>
+        <v>1318</v>
       </c>
       <c r="C4" t="n">
-        <v>8003</v>
+        <v>10083</v>
       </c>
       <c r="D4" t="n">
-        <v>14526</v>
+        <v>9264</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1657</v>
+        <v>591</v>
       </c>
       <c r="C5" t="n">
-        <v>8065</v>
+        <v>13763</v>
       </c>
       <c r="D5" t="n">
-        <v>5835</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>795</v>
+        <v>192</v>
       </c>
       <c r="C6" t="n">
-        <v>4750</v>
+        <v>8449</v>
       </c>
       <c r="D6" t="n">
-        <v>1559</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>2451</v>
+        <v>2655</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>982</v>
+        <v>730</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3329</v>
+        <v>268</v>
       </c>
       <c r="C2" t="n">
-        <v>5232</v>
+        <v>4178</v>
       </c>
       <c r="D2" t="n">
-        <v>14529</v>
+        <v>7877</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2920</v>
+        <v>590</v>
       </c>
       <c r="C3" t="n">
-        <v>3156</v>
+        <v>6178</v>
       </c>
       <c r="D3" t="n">
-        <v>17788</v>
+        <v>10818</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3060</v>
+        <v>919</v>
       </c>
       <c r="C4" t="n">
-        <v>6388</v>
+        <v>8229</v>
       </c>
       <c r="D4" t="n">
-        <v>14859</v>
+        <v>8975</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2014</v>
+        <v>599</v>
       </c>
       <c r="C5" t="n">
-        <v>7947</v>
+        <v>10683</v>
       </c>
       <c r="D5" t="n">
-        <v>6909</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1018</v>
+        <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>6122</v>
+        <v>8644</v>
       </c>
       <c r="D6" t="n">
-        <v>2113</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>42</v>
       </c>
       <c r="C7" t="n">
-        <v>3399</v>
+        <v>3440</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1519</v>
+        <v>861</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>501</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>109</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2258</v>
+        <v>432</v>
       </c>
       <c r="C2" t="n">
-        <v>2960</v>
+        <v>6025</v>
       </c>
       <c r="D2" t="n">
-        <v>11374</v>
+        <v>10740</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2673</v>
+        <v>380</v>
       </c>
       <c r="C3" t="n">
-        <v>3598</v>
+        <v>4592</v>
       </c>
       <c r="D3" t="n">
-        <v>16600</v>
+        <v>9650</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>678</v>
       </c>
       <c r="C4" t="n">
-        <v>5135</v>
+        <v>7014</v>
       </c>
       <c r="D4" t="n">
-        <v>14915</v>
+        <v>9020</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2211</v>
+        <v>664</v>
       </c>
       <c r="C5" t="n">
-        <v>7533</v>
+        <v>9259</v>
       </c>
       <c r="D5" t="n">
-        <v>7604</v>
+        <v>4927</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1185</v>
+        <v>321</v>
       </c>
       <c r="C6" t="n">
-        <v>6924</v>
+        <v>9599</v>
       </c>
       <c r="D6" t="n">
-        <v>2564</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>4271</v>
+        <v>5784</v>
       </c>
       <c r="D7" t="n">
-        <v>825</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1953</v>
+        <v>1981</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>571</v>
+        <v>492</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3426</v>
+        <v>756</v>
       </c>
       <c r="C2" t="n">
-        <v>5012</v>
+        <v>11105</v>
       </c>
       <c r="D2" t="n">
-        <v>13034</v>
+        <v>10095</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2130</v>
+        <v>332</v>
       </c>
       <c r="C3" t="n">
-        <v>2976</v>
+        <v>4605</v>
       </c>
       <c r="D3" t="n">
-        <v>14910</v>
+        <v>9156</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2383</v>
+        <v>487</v>
       </c>
       <c r="C4" t="n">
-        <v>4378</v>
+        <v>5752</v>
       </c>
       <c r="D4" t="n">
-        <v>14704</v>
+        <v>8755</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2190</v>
+        <v>612</v>
       </c>
       <c r="C5" t="n">
-        <v>6409</v>
+        <v>8075</v>
       </c>
       <c r="D5" t="n">
-        <v>8355</v>
+        <v>5405</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1421</v>
+        <v>413</v>
       </c>
       <c r="C6" t="n">
-        <v>7099</v>
+        <v>9273</v>
       </c>
       <c r="D6" t="n">
-        <v>3160</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>487</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>5299</v>
+        <v>7389</v>
       </c>
       <c r="D7" t="n">
-        <v>1021</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>2747</v>
+        <v>3508</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1023</v>
+        <v>1060</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>278</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5161</v>
+        <v>4883</v>
       </c>
       <c r="C2" t="n">
-        <v>6356</v>
+        <v>20746</v>
       </c>
       <c r="D2" t="n">
-        <v>18276</v>
+        <v>9429</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2450</v>
+        <v>609</v>
       </c>
       <c r="C2" t="n">
-        <v>2886</v>
+        <v>23976</v>
       </c>
       <c r="D2" t="n">
-        <v>9594</v>
+        <v>11923</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2887</v>
+        <v>395</v>
       </c>
       <c r="C3" t="n">
-        <v>3693</v>
+        <v>6384</v>
       </c>
       <c r="D3" t="n">
-        <v>16135</v>
+        <v>8770</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3241</v>
+        <v>372</v>
       </c>
       <c r="C4" t="n">
-        <v>6518</v>
+        <v>5114</v>
       </c>
       <c r="D4" t="n">
-        <v>15132</v>
+        <v>8458</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1353</v>
+        <v>519</v>
       </c>
       <c r="C5" t="n">
-        <v>9687</v>
+        <v>6915</v>
       </c>
       <c r="D5" t="n">
-        <v>7563</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="6">
@@ -4260,10 +4260,10 @@
         <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>6584</v>
+        <v>8735</v>
       </c>
       <c r="D6" t="n">
-        <v>2418</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="C7" t="n">
-        <v>2692</v>
+        <v>8015</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1002</v>
+        <v>4913</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>316</v>
+        <v>1888</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>538</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6221</v>
+        <v>4532</v>
       </c>
       <c r="C2" t="n">
-        <v>5151</v>
+        <v>17295</v>
       </c>
       <c r="D2" t="n">
-        <v>33152</v>
+        <v>25226</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2193</v>
+        <v>1575</v>
       </c>
       <c r="C3" t="n">
-        <v>3203</v>
+        <v>8192</v>
       </c>
       <c r="D3" t="n">
-        <v>3709</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4753</v>
+        <v>2313</v>
       </c>
       <c r="C2" t="n">
-        <v>5049</v>
+        <v>9862</v>
       </c>
       <c r="D2" t="n">
-        <v>28277</v>
+        <v>26170</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3453</v>
+        <v>2552</v>
       </c>
       <c r="C3" t="n">
-        <v>3712</v>
+        <v>11686</v>
       </c>
       <c r="D3" t="n">
-        <v>8382</v>
+        <v>5866</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>987</v>
+        <v>741</v>
       </c>
       <c r="C4" t="n">
-        <v>1921</v>
+        <v>5082</v>
       </c>
       <c r="D4" t="n">
-        <v>1928</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6185</v>
+        <v>1795</v>
       </c>
       <c r="C2" t="n">
-        <v>7271</v>
+        <v>7714</v>
       </c>
       <c r="D2" t="n">
-        <v>22784</v>
+        <v>20861</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3363</v>
+        <v>2030</v>
       </c>
       <c r="C3" t="n">
-        <v>3839</v>
+        <v>9187</v>
       </c>
       <c r="D3" t="n">
-        <v>10961</v>
+        <v>8901</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1887</v>
+        <v>1409</v>
       </c>
       <c r="C4" t="n">
-        <v>2859</v>
+        <v>8843</v>
       </c>
       <c r="D4" t="n">
-        <v>3108</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>457</v>
+        <v>357</v>
       </c>
       <c r="C5" t="n">
-        <v>1148</v>
+        <v>2964</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>791</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5471</v>
+        <v>2443</v>
       </c>
       <c r="C2" t="n">
-        <v>6906</v>
+        <v>6981</v>
       </c>
       <c r="D2" t="n">
-        <v>30668</v>
+        <v>26385</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3823</v>
+        <v>1591</v>
       </c>
       <c r="C3" t="n">
-        <v>4879</v>
+        <v>7309</v>
       </c>
       <c r="D3" t="n">
-        <v>11986</v>
+        <v>10092</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2202</v>
+        <v>1461</v>
       </c>
       <c r="C4" t="n">
-        <v>3326</v>
+        <v>8847</v>
       </c>
       <c r="D4" t="n">
-        <v>4445</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>964</v>
+        <v>736</v>
       </c>
       <c r="C5" t="n">
-        <v>2011</v>
+        <v>6006</v>
       </c>
       <c r="D5" t="n">
-        <v>1547</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="C6" t="n">
-        <v>720</v>
+        <v>1634</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>297</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>303</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5532</v>
+        <v>2766</v>
       </c>
       <c r="C2" t="n">
-        <v>8155</v>
+        <v>13776</v>
       </c>
       <c r="D2" t="n">
-        <v>42138</v>
+        <v>22894</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3364</v>
+        <v>1619</v>
       </c>
       <c r="C3" t="n">
-        <v>4845</v>
+        <v>6257</v>
       </c>
       <c r="D3" t="n">
-        <v>13154</v>
+        <v>11743</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1867</v>
+        <v>1318</v>
       </c>
       <c r="C4" t="n">
-        <v>3425</v>
+        <v>7880</v>
       </c>
       <c r="D4" t="n">
-        <v>4958</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>817</v>
+        <v>924</v>
       </c>
       <c r="C5" t="n">
-        <v>1966</v>
+        <v>7272</v>
       </c>
       <c r="D5" t="n">
-        <v>1608</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>393</v>
       </c>
       <c r="C6" t="n">
-        <v>909</v>
+        <v>3657</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>341</v>
+        <v>925</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4534</v>
+        <v>2727</v>
       </c>
       <c r="C2" t="n">
-        <v>5865</v>
+        <v>15467</v>
       </c>
       <c r="D2" t="n">
-        <v>37652</v>
+        <v>26295</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3677</v>
+        <v>1734</v>
       </c>
       <c r="C3" t="n">
-        <v>5831</v>
+        <v>8463</v>
       </c>
       <c r="D3" t="n">
-        <v>17055</v>
+        <v>12470</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2269</v>
+        <v>1236</v>
       </c>
       <c r="C4" t="n">
-        <v>4212</v>
+        <v>6952</v>
       </c>
       <c r="D4" t="n">
-        <v>6411</v>
+        <v>5502</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1196</v>
+        <v>967</v>
       </c>
       <c r="C5" t="n">
-        <v>2779</v>
+        <v>7395</v>
       </c>
       <c r="D5" t="n">
-        <v>2234</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>510</v>
+        <v>556</v>
       </c>
       <c r="C6" t="n">
-        <v>1496</v>
+        <v>5148</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>658</v>
+        <v>2102</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>285</v>
+        <v>554</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5340</v>
+        <v>2521</v>
       </c>
       <c r="C2" t="n">
-        <v>7674</v>
+        <v>10146</v>
       </c>
       <c r="D2" t="n">
-        <v>28962</v>
+        <v>21184</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3370</v>
+        <v>2190</v>
       </c>
       <c r="C3" t="n">
-        <v>5072</v>
+        <v>13021</v>
       </c>
       <c r="D3" t="n">
-        <v>19122</v>
+        <v>13459</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2528</v>
+        <v>893</v>
       </c>
       <c r="C4" t="n">
-        <v>5025</v>
+        <v>11103</v>
       </c>
       <c r="D4" t="n">
-        <v>8259</v>
+        <v>4985</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1516</v>
+        <v>513</v>
       </c>
       <c r="C5" t="n">
-        <v>3464</v>
+        <v>5045</v>
       </c>
       <c r="D5" t="n">
-        <v>2927</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>761</v>
+        <v>194</v>
       </c>
       <c r="C6" t="n">
-        <v>2156</v>
+        <v>2059</v>
       </c>
       <c r="D6" t="n">
-        <v>1148</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1092</v>
+        <v>542</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>471</v>
+        <v>275</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
